--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>83.38252602003696</v>
+        <v>13.54966047825601</v>
       </c>
       <c r="D2" t="n">
-        <v>82.85919529355579</v>
+        <v>13.46461923520282</v>
       </c>
       <c r="E2" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F2" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.39536009445642</v>
+        <v>8.189246015349168</v>
       </c>
       <c r="D3" t="n">
-        <v>50.13903690429637</v>
+        <v>8.14759349694816</v>
       </c>
       <c r="E3" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F3" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.46743263530597</v>
+        <v>9.988457803237219</v>
       </c>
       <c r="D4" t="n">
-        <v>60.93585307283372</v>
+        <v>9.90207612433548</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F4" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.85587362824294</v>
+        <v>7.289079464589478</v>
       </c>
       <c r="D5" t="n">
-        <v>44.28234250443383</v>
+        <v>7.195880656970497</v>
       </c>
       <c r="E5" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F5" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>73.56905654168462</v>
+        <v>11.95497168802375</v>
       </c>
       <c r="D6" t="n">
-        <v>73.11334088095148</v>
+        <v>11.88091789315462</v>
       </c>
       <c r="E6" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F6" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.01536398316316</v>
+        <v>8.289996647264013</v>
       </c>
       <c r="D7" t="n">
-        <v>50.51111112003641</v>
+        <v>8.208055557005917</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F7" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.13759468364485</v>
+        <v>6.034859136092289</v>
       </c>
       <c r="D8" t="n">
-        <v>36.99592728470184</v>
+        <v>6.011838183764048</v>
       </c>
       <c r="E8" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F8" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.27655297984027</v>
+        <v>6.219939859224044</v>
       </c>
       <c r="D9" t="n">
-        <v>37.74223298882988</v>
+        <v>6.133112860684856</v>
       </c>
       <c r="E9" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F9" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.5806083664674</v>
+        <v>7.406848859550953</v>
       </c>
       <c r="D10" t="n">
-        <v>45.55447759393315</v>
+        <v>7.402602609014137</v>
       </c>
       <c r="E10" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F10" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.00849983139857</v>
+        <v>2.763881222602268</v>
       </c>
       <c r="D11" t="n">
-        <v>16.43305368473774</v>
+        <v>2.670371223769883</v>
       </c>
       <c r="E11" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F11" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.66220569675617</v>
+        <v>5.632608425722879</v>
       </c>
       <c r="D12" t="n">
-        <v>34.90699949128273</v>
+        <v>5.672387417333444</v>
       </c>
       <c r="E12" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F12" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.60561959516791</v>
+        <v>7.248413184214785</v>
       </c>
       <c r="D13" t="n">
-        <v>44.35872355892303</v>
+        <v>7.208292578324992</v>
       </c>
       <c r="E13" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F13" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>72.09733625871344</v>
+        <v>11.71581714204093</v>
       </c>
       <c r="D14" t="n">
-        <v>71.87566456163219</v>
+        <v>11.67979549126523</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F14" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.01284589356042</v>
+        <v>5.039587457703568</v>
       </c>
       <c r="D15" t="n">
-        <v>30.95121823052962</v>
+        <v>5.029572962461063</v>
       </c>
       <c r="E15" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F15" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.68048067102454</v>
+        <v>9.048078109041487</v>
       </c>
       <c r="D16" t="n">
-        <v>55.54748771917461</v>
+        <v>9.026466754365874</v>
       </c>
       <c r="E16" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F16" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>57.82824085595552</v>
+        <v>9.397089139092772</v>
       </c>
       <c r="D17" t="n">
-        <v>58.24379211393097</v>
+        <v>9.464616218513783</v>
       </c>
       <c r="E17" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F17" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>43.61780950415614</v>
+        <v>7.087894044425373</v>
       </c>
       <c r="D18" t="n">
-        <v>44.10507951030149</v>
+        <v>7.167075420423992</v>
       </c>
       <c r="E18" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F18" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>29.01846046427623</v>
+        <v>4.715499825444888</v>
       </c>
       <c r="D19" t="n">
-        <v>29.57116266374491</v>
+        <v>4.805313932858549</v>
       </c>
       <c r="E19" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F19" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>38.22404384746788</v>
+        <v>6.21140712521353</v>
       </c>
       <c r="D20" t="n">
-        <v>38.41286298403855</v>
+        <v>6.242090234906265</v>
       </c>
       <c r="E20" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F20" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>40.55241444194417</v>
+        <v>6.589767346815928</v>
       </c>
       <c r="D21" t="n">
-        <v>40.99537807076032</v>
+        <v>6.661748936498553</v>
       </c>
       <c r="E21" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F21" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>66.21659284101182</v>
+        <v>10.76019633666442</v>
       </c>
       <c r="D22" t="n">
-        <v>66.75777291075558</v>
+        <v>10.84813809799778</v>
       </c>
       <c r="E22" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F22" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>51.53230437062696</v>
+        <v>8.373999460226882</v>
       </c>
       <c r="D23" t="n">
-        <v>52.00920106052424</v>
+        <v>8.451495172335189</v>
       </c>
       <c r="E23" t="n">
-        <v>15.6284945702022</v>
+        <v>2.539630367657858</v>
       </c>
       <c r="F23" t="n">
-        <v>15.56922031523849</v>
+        <v>2.529998301226254</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
